--- a/artfynd/A 3519-2025 artfynd.xlsx
+++ b/artfynd/A 3519-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73967992</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100679</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471516.3496863065</v>
+        <v>471516</v>
       </c>
       <c r="R2" t="n">
-        <v>6399996.124827122</v>
+        <v>6399996</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74478572</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471516.3496863065</v>
+        <v>471516</v>
       </c>
       <c r="R3" t="n">
-        <v>6399996.124827122</v>
+        <v>6399996</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74552177</v>
       </c>
       <c r="B4" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471516.3496863065</v>
+        <v>471516</v>
       </c>
       <c r="R4" t="n">
-        <v>6399996.124827122</v>
+        <v>6399996</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1056,12 +1011,7 @@
         <v>74766383</v>
       </c>
       <c r="B5" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471516.3496863065</v>
+        <v>471516</v>
       </c>
       <c r="R5" t="n">
-        <v>6399996.124827122</v>
+        <v>6399996</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1126,19 +1076,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 3519-2025 artfynd.xlsx
+++ b/artfynd/A 3519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73967992</v>
       </c>
       <c r="B2" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74478572</v>
       </c>
       <c r="B3" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74552177</v>
       </c>
       <c r="B4" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74766383</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3519-2025 artfynd.xlsx
+++ b/artfynd/A 3519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73967992</v>
       </c>
       <c r="B2" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74478572</v>
       </c>
       <c r="B3" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74552177</v>
       </c>
       <c r="B4" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74766383</v>
       </c>
       <c r="B5" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3519-2025 artfynd.xlsx
+++ b/artfynd/A 3519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73967992</v>
       </c>
       <c r="B2" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74478572</v>
       </c>
       <c r="B3" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74552177</v>
       </c>
       <c r="B4" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74766383</v>
       </c>
       <c r="B5" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3519-2025 artfynd.xlsx
+++ b/artfynd/A 3519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73967992</v>
       </c>
       <c r="B2" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74478572</v>
       </c>
       <c r="B3" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74552177</v>
       </c>
       <c r="B4" t="n">
-        <v>101712</v>
+        <v>101718</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74766383</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3519-2025 artfynd.xlsx
+++ b/artfynd/A 3519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73967992</v>
       </c>
       <c r="B2" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74478572</v>
       </c>
       <c r="B3" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74552177</v>
       </c>
       <c r="B4" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74766383</v>
       </c>
       <c r="B5" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3519-2025 artfynd.xlsx
+++ b/artfynd/A 3519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73967992</v>
       </c>
       <c r="B2" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74478572</v>
       </c>
       <c r="B3" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74552177</v>
       </c>
       <c r="B4" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74766383</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3519-2025 artfynd.xlsx
+++ b/artfynd/A 3519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73967992</v>
       </c>
       <c r="B2" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74478572</v>
       </c>
       <c r="B3" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74552177</v>
       </c>
       <c r="B4" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74766383</v>
       </c>
       <c r="B5" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3519-2025 artfynd.xlsx
+++ b/artfynd/A 3519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73967992</v>
       </c>
       <c r="B2" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74478572</v>
       </c>
       <c r="B3" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74552177</v>
       </c>
       <c r="B4" t="n">
-        <v>101739</v>
+        <v>101744</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74766383</v>
       </c>
       <c r="B5" t="n">
-        <v>98683</v>
+        <v>98688</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3519-2025 artfynd.xlsx
+++ b/artfynd/A 3519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73967992</v>
       </c>
       <c r="B2" t="n">
-        <v>100745</v>
+        <v>100753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74478572</v>
       </c>
       <c r="B3" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74552177</v>
       </c>
       <c r="B4" t="n">
-        <v>101744</v>
+        <v>101752</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74766383</v>
       </c>
       <c r="B5" t="n">
-        <v>98688</v>
+        <v>98696</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3519-2025 artfynd.xlsx
+++ b/artfynd/A 3519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73967992</v>
       </c>
       <c r="B2" t="n">
-        <v>100753</v>
+        <v>100763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74478572</v>
       </c>
       <c r="B3" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74552177</v>
       </c>
       <c r="B4" t="n">
-        <v>101752</v>
+        <v>101762</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74766383</v>
       </c>
       <c r="B5" t="n">
-        <v>98696</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3519-2025 artfynd.xlsx
+++ b/artfynd/A 3519-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73967992</v>
+        <v>74766383</v>
       </c>
       <c r="B2" t="n">
-        <v>100763</v>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E0e 2535. SOM: Actaea spicata. LEG: Inger Bergqvist,  Torsten Karlsson</t>
+          <t>Smålands flora 2007: KOO: 7E0e 2535. SOM: Platanthera chlorantha. LEG: Inger Bergqvist, Torsten Karlsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blandskogsbrant</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74478572</v>
+        <v>74552177</v>
       </c>
       <c r="B3" t="n">
-        <v>100857</v>
+        <v>102240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E0e 2535. SOM: Hepatica nobilis. LEG: Inger Bergqvist, Torsten Karlsson</t>
+          <t>Smålands flora 2007: KOO: 7E0e 2535. SOM: Lathyrus vernus. LEG: Inger Bergqvist, Torsten Karlsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74552177</v>
+        <v>74478572</v>
       </c>
       <c r="B4" t="n">
-        <v>101762</v>
+        <v>101325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E0e 2535. SOM: Lathyrus vernus. LEG: Inger Bergqvist, Torsten Karlsson</t>
+          <t>Smålands flora 2007: KOO: 7E0e 2535. SOM: Hepatica nobilis. LEG: Inger Bergqvist, Torsten Karlsson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74766383</v>
+        <v>73967992</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>101227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219875</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E0e 2535. SOM: Platanthera chlorantha. LEG: Inger Bergqvist, Torsten Karlsson</t>
+          <t>Smålands flora 2007: KOO: 7E0e 2535. SOM: Actaea spicata. LEG: Inger Bergqvist,  Torsten Karlsson</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Blandskogsbrant</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 3519-2025 artfynd.xlsx
+++ b/artfynd/A 3519-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74766383</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74552177</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74478572</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,8 +1136,19 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73967992</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>